--- a/Build/BOM.xlsx
+++ b/Build/BOM.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\StepperDriver\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F275A6E3-C8F4-478A-9783-E8C866310B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{475B62B3-2FEF-4CB8-B0F9-4B78E714DF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{1689F00D-B39B-4009-A3A0-4BE00F28B780}"/>
+    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{428832CA-AF1F-4C30-A1F5-7B3B3CA438EE}"/>
   </bookViews>
   <sheets>
-    <sheet name="BOM" sheetId="1" r:id="rId1"/>
+    <sheet name="StepperDriver" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="93">
   <si>
     <t>Reference</t>
   </si>
@@ -150,7 +150,7 @@
     <t>C15849</t>
   </si>
   <si>
-    <t>D1,D2,D3</t>
+    <t>D1,D2,D4</t>
   </si>
   <si>
     <t>DSK24</t>
@@ -162,7 +162,7 @@
     <t>C22466352</t>
   </si>
   <si>
-    <t>D4</t>
+    <t>D3</t>
   </si>
   <si>
     <t>SMF40CA</t>
@@ -183,7 +183,7 @@
     <t>C167974</t>
   </si>
   <si>
-    <t>R1,R9,R10,R11,R12,R13,R14,R15</t>
+    <t>R1,R3,R10,R11,R12,R13,R14,R15</t>
   </si>
   <si>
     <t>10K</t>
@@ -210,7 +210,7 @@
     <t>C22978</t>
   </si>
   <si>
-    <t>R3</t>
+    <t>R4</t>
   </si>
   <si>
     <t>22K</t>
@@ -222,7 +222,7 @@
     <t>C31850</t>
   </si>
   <si>
-    <t>R4,R5</t>
+    <t>R5,R6</t>
   </si>
   <si>
     <t>100m</t>
@@ -237,7 +237,7 @@
     <t>C25334</t>
   </si>
   <si>
-    <t>R6,R7</t>
+    <t>R7,R8</t>
   </si>
   <si>
     <t>2.2K</t>
@@ -249,7 +249,7 @@
     <t>C4190</t>
   </si>
   <si>
-    <t>R8</t>
+    <t>R9</t>
   </si>
   <si>
     <t>1K</t>
@@ -261,10 +261,10 @@
     <t>C21190</t>
   </si>
   <si>
-    <t>SW1</t>
-  </si>
-  <si>
-    <t>SW_M</t>
+    <t>SW1,SW2,SW3</t>
+  </si>
+  <si>
+    <t>SPST_TS</t>
   </si>
   <si>
     <t>Button_Switch_SMD:SW_SPST_TS-1088-xR020</t>
@@ -274,18 +274,6 @@
   </si>
   <si>
     <t>C720477</t>
-  </si>
-  <si>
-    <t>SW2</t>
-  </si>
-  <si>
-    <t>SW_C</t>
-  </si>
-  <si>
-    <t>SW3</t>
-  </si>
-  <si>
-    <t>SW_P</t>
   </si>
   <si>
     <t>U1</t>
@@ -1175,8 +1163,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0ED5B03-F058-4E9B-81F3-BF7F26749ACA}">
-  <dimension ref="A1:F23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3687A96E-2B70-43B5-B3AA-E21B09065904}">
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1544,7 +1532,7 @@
         <v>78</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
         <v>79</v>
@@ -1570,73 +1558,33 @@
         <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
         <v>92</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Build/BOM.xlsx
+++ b/Build/BOM.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\StepperDriver\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{475B62B3-2FEF-4CB8-B0F9-4B78E714DF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5D38E32-6C69-4EB8-90F3-1B18050E8E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{428832CA-AF1F-4C30-A1F5-7B3B3CA438EE}"/>
+    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{10475209-4FD1-4E30-BA14-6F080A973154}"/>
   </bookViews>
   <sheets>
-    <sheet name="StepperDriver" sheetId="1" r:id="rId1"/>
+    <sheet name="BOM" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="98">
   <si>
     <t>Reference</t>
   </si>
@@ -171,6 +171,21 @@
     <t>C42371749</t>
   </si>
   <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>RED</t>
+  </si>
+  <si>
+    <t>LED_SMD:LED_0603_1608Metric</t>
+  </si>
+  <si>
+    <t>KT-0603R</t>
+  </si>
+  <si>
+    <t>C2286</t>
+  </si>
+  <si>
     <t>L1</t>
   </si>
   <si>
@@ -183,7 +198,7 @@
     <t>C167974</t>
   </si>
   <si>
-    <t>R1,R3,R10,R11,R12,R13,R14,R15</t>
+    <t>R1,R3,R10,R11,R12,R14,R15,R16</t>
   </si>
   <si>
     <t>10K</t>
@@ -237,7 +252,7 @@
     <t>C25334</t>
   </si>
   <si>
-    <t>R7,R8</t>
+    <t>R7,R8,R13</t>
   </si>
   <si>
     <t>2.2K</t>
@@ -294,16 +309,16 @@
     <t>U2</t>
   </si>
   <si>
-    <t>TMC2208-LA</t>
-  </si>
-  <si>
-    <t>Custom_Parts:QFN-28-1EP_5x5mm_P0.5mm_EP3.1x3.1mm_ThermalVias</t>
-  </si>
-  <si>
-    <t>TMC2208-LA-T</t>
-  </si>
-  <si>
-    <t>C115944</t>
+    <t>TMC2209-LA</t>
+  </si>
+  <si>
+    <t>Custom_Parts:VQFN-28-1EP_5x5mm_P0.5mm_EP3.7x3.7mm_ThermalVias</t>
+  </si>
+  <si>
+    <t>TMC2209-LA-T</t>
+  </si>
+  <si>
+    <t>C2150710</t>
   </si>
 </sst>
 </file>
@@ -1163,8 +1178,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3687A96E-2B70-43B5-B3AA-E21B09065904}">
-  <dimension ref="A1:F21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98990E5A-DBC1-485F-8A6B-BBC3DFCD5D0F}">
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1395,27 +1410,27 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -1432,53 +1447,53 @@
         <v>57</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
         <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
@@ -1498,47 +1513,47 @@
         <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
         <v>81</v>
@@ -1552,7 +1567,7 @@
         <v>83</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" t="s">
         <v>84</v>
@@ -1585,6 +1600,26 @@
       </c>
       <c r="F21" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Build/BOM.xlsx
+++ b/Build/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\StepperDriver\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5D38E32-6C69-4EB8-90F3-1B18050E8E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6460E8F0-5326-4832-A5D2-86ED705569D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{10475209-4FD1-4E30-BA14-6F080A973154}"/>
+    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{E8450DFE-EB55-497C-836E-51FB0BDB14F4}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -66,13 +66,13 @@
     <t>47u</t>
   </si>
   <si>
-    <t>Capacitor_SMD:CP_Elec_6.3x5.4</t>
-  </si>
-  <si>
-    <t>SM476M050E0800</t>
-  </si>
-  <si>
-    <t>C44606723</t>
+    <t>Capacitor_SMD:CP_Elec_6.3x5.8</t>
+  </si>
+  <si>
+    <t>HV1V476M0605PZ</t>
+  </si>
+  <si>
+    <t>C5246552</t>
   </si>
   <si>
     <t>C6,C18,C19,C20</t>
@@ -1178,7 +1178,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98990E5A-DBC1-485F-8A6B-BBC3DFCD5D0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4CEBCED-1A95-4949-87C6-7462F0B048AD}">
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>

--- a/Build/BOM.xlsx
+++ b/Build/BOM.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\StepperDriver\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6460E8F0-5326-4832-A5D2-86ED705569D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{12B2A747-8065-4954-8925-7146E3F2256D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{E8450DFE-EB55-497C-836E-51FB0BDB14F4}"/>
+    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{A1F2E9F3-67C9-4A0D-9A77-38D6800BC0EC}"/>
   </bookViews>
   <sheets>
-    <sheet name="BOM" sheetId="1" r:id="rId1"/>
+    <sheet name="StepperDriver" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -267,13 +267,13 @@
     <t>R9</t>
   </si>
   <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>0603WAF1001T5E</t>
-  </si>
-  <si>
-    <t>C21190</t>
+    <t>0R</t>
+  </si>
+  <si>
+    <t>0603WAF0000T5E</t>
+  </si>
+  <si>
+    <t>C21189</t>
   </si>
   <si>
     <t>SW1,SW2,SW3</t>
@@ -1178,7 +1178,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4CEBCED-1A95-4949-87C6-7462F0B048AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A9062B-C970-4B21-98CD-F318E20BCDD8}">
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>

--- a/Build/BOM.xlsx
+++ b/Build/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\StepperDriver\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12B2A747-8065-4954-8925-7146E3F2256D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C55A17A3-1C29-4FC7-B7AA-A9F2CD3D9BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{A1F2E9F3-67C9-4A0D-9A77-38D6800BC0EC}"/>
+    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{901A9B37-6115-42E0-9B59-27C03A6FD18F}"/>
   </bookViews>
   <sheets>
     <sheet name="StepperDriver" sheetId="1" r:id="rId1"/>
@@ -69,10 +69,10 @@
     <t>Capacitor_SMD:CP_Elec_6.3x5.8</t>
   </si>
   <si>
-    <t>HV1V476M0605PZ</t>
-  </si>
-  <si>
-    <t>C5246552</t>
+    <t>SVZ1VM470E06E00RAXXX</t>
+  </si>
+  <si>
+    <t>C721322</t>
   </si>
   <si>
     <t>C6,C18,C19,C20</t>
@@ -1178,7 +1178,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A9062B-C970-4B21-98CD-F318E20BCDD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A441D1E-CB3F-49EB-8F83-51E706BC9BAF}">
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
